--- a/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
+++ b/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE21D915-8755-44EF-AE1F-3AFE0055799A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79C904EA-CAE7-4C0B-BB97-AF581CA74341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="18" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="17" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="16" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="15" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="14" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1438,7 +1438,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D7213A-AD16-F878-79B7-1D92229FF59A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2D24525-7A10-8D26-98D4-37F089271E0E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1493,7 +1493,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76DE3B01-58B5-BE00-D067-226E92142F5F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15131C5D-DF70-34AA-7F4C-B44D0AE2D9AA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1844,7 +1844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0F7639-F0D6-4AB9-A36B-C2E510D101B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F0D7CCB-3E9E-4111-B8CA-A37F9C023719}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4972,7 +4972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AC5056-541C-4C56-B8CD-41AEEAFFF3BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D007B33-FE77-44AA-8664-AAF1B7C85B44}">
   <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5582,7 +5582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD43DC34-2F2D-46B2-AB89-F8D6D5366D55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B83BC5-D416-402B-8391-8FB847FD4045}">
   <dimension ref="B2:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5858,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507C8BE0-68A2-4794-8C11-7A49C0D70E7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86798CCC-8915-48C8-B324-73F9CF504FDF}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6313,7 +6313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BC1F0BF-8E7E-44B3-96DF-A65A57B0445C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2062861-EDE4-46D5-A2E5-77308F5FD7EB}">
   <dimension ref="A1:Y115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
+++ b/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54F454FF-FF5D-43DB-935C-C31857C9F02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE5B1CB0-CA77-4B28-A1B4-13C4E2B6EC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="33" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="32" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="31" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="30" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="29" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="38" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="37" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="36" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="35" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="34" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3077" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="417">
   <si>
     <t>power plants size threshold for individual representation</t>
   </si>
@@ -1128,34 +1128,193 @@
     <t xml:space="preserve">Stated Policies </t>
   </si>
   <si>
-    <t>ELC</t>
-  </si>
-  <si>
-    <t>en_pc_bioenergy</t>
-  </si>
-  <si>
-    <t>ep_bioenergy</t>
-  </si>
-  <si>
-    <t>ep_bioenergy__irena</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>ep_geothermal</t>
-  </si>
-  <si>
-    <t>ep_geothermal__irena</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap_Missing Geothermal Capacity -- operating</t>
-  </si>
-  <si>
-    <t>ep_hydro__irena</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap_Missing Hydro Capacity -- operating</t>
+    <t>e_w457973270-400</t>
+  </si>
+  <si>
+    <t>w457973270-400</t>
+  </si>
+  <si>
+    <t>e_w569997185-400</t>
+  </si>
+  <si>
+    <t>w569997185-400</t>
+  </si>
+  <si>
+    <t>e_w579310367-220</t>
+  </si>
+  <si>
+    <t>w579310367-220</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220</t>
+  </si>
+  <si>
+    <t>w1115312336-220</t>
+  </si>
+  <si>
+    <t>e_KE12-400</t>
+  </si>
+  <si>
+    <t>KE12-400</t>
+  </si>
+  <si>
+    <t>en_pc_bioenergy_w86402221-220</t>
+  </si>
+  <si>
+    <t>e_w86402221-220</t>
+  </si>
+  <si>
+    <t>w86402221-220</t>
+  </si>
+  <si>
+    <t>e_KE4-220</t>
+  </si>
+  <si>
+    <t>KE4-220</t>
+  </si>
+  <si>
+    <t>e_w846713577-220</t>
+  </si>
+  <si>
+    <t>w846713577-220</t>
+  </si>
+  <si>
+    <t>e_w669510376-220</t>
+  </si>
+  <si>
+    <t>w669510376-220</t>
+  </si>
+  <si>
+    <t>e_w457973270-220</t>
+  </si>
+  <si>
+    <t>w457973270-220</t>
+  </si>
+  <si>
+    <t>e_KE1-220</t>
+  </si>
+  <si>
+    <t>KE1-220</t>
+  </si>
+  <si>
+    <t>e_w669520367-220</t>
+  </si>
+  <si>
+    <t>w669520367-220</t>
+  </si>
+  <si>
+    <t>e_KE6-220</t>
+  </si>
+  <si>
+    <t>KE6-220</t>
+  </si>
+  <si>
+    <t>e_w659874569-220</t>
+  </si>
+  <si>
+    <t>w659874569-220</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_KE2-220</t>
+  </si>
+  <si>
+    <t>e_KE2-220</t>
+  </si>
+  <si>
+    <t>KE2-220</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_KE2-220__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w86402221-220__irena</t>
+  </si>
+  <si>
+    <t>e_KE7-220</t>
+  </si>
+  <si>
+    <t>KE7-220</t>
+  </si>
+  <si>
+    <t>ep_geothermal_KE7-220__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - KE7-220_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>ep_geothermal_w457973270-400</t>
+  </si>
+  <si>
+    <t>ep_geothermal_w457973270-400__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/457973270-400_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>ep_geothermal_w569997185-400__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/569997185-400_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>ep_geothermal_w669510376-220__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/669510376-220_Missing Geothermal Capacity -- operating</t>
+  </si>
+  <si>
+    <t>ep_hydro_KE6-220__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - KE6-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>e_w220540545-220</t>
+  </si>
+  <si>
+    <t>w220540545-220</t>
+  </si>
+  <si>
+    <t>ep_hydro_w1115312336-220__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/1115312336-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>ep_hydro_w669520367-220__irena</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/669520367-220_Missing Hydro Capacity -- operating</t>
+  </si>
+  <si>
+    <t>e_KE9-220</t>
+  </si>
+  <si>
+    <t>KE9-220</t>
+  </si>
+  <si>
+    <t>e_w953567827-220</t>
+  </si>
+  <si>
+    <t>w953567827-220</t>
+  </si>
+  <si>
+    <t>e_KE15-220</t>
+  </si>
+  <si>
+    <t>KE15-220</t>
+  </si>
+  <si>
+    <t>e_KE10-220</t>
+  </si>
+  <si>
+    <t>KE10-220</t>
+  </si>
+  <si>
+    <t>e_KE11-220</t>
+  </si>
+  <si>
+    <t>KE11-220</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1438,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAE45189-E897-93DD-63AF-39CF52131A32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94689CB2-40D7-8D8C-F753-FF4F04ECEA98}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1334,7 +1493,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E90AE61-4D3D-E0AC-AD80-E3D3F051D670}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB90FBAE-984D-EE28-6E99-EAE3AE39B7F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1685,7 +1844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B7629F-D537-4697-9142-B5E62B5C0CEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A6B2D4-B78E-47AD-96A4-D2DA35248C0C}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4813,7 +4972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF9560F-519E-4C8F-B4F5-67A2546358CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A268F1-7B72-4A73-A2E6-D8552CD961AF}">
   <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5423,7 +5582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F930766F-202B-4C59-B7FA-08D5DED4C24D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523B0D75-838B-446A-A3FF-CFFC6BDAD3A2}">
   <dimension ref="B2:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5699,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC1D818-8C73-4424-B1AB-6E01D1AF3645}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A637E6B6-466B-4A36-B060-72618466DD4E}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6020,7 +6179,7 @@
         <v>0.63</v>
       </c>
       <c r="E27">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="F27">
         <v>0.9</v>
@@ -6154,8 +6313,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC29B9D-A26B-4EF9-BE8E-921221C3AA29}">
-  <dimension ref="A1:Y109"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89704539-7958-4D2A-B729-A9BD7F41AF1C}">
+  <dimension ref="A1:Y115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:25" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
@@ -6292,6 +6451,9 @@
       <c r="J7" t="s">
         <v>354</v>
       </c>
+      <c r="K7" t="s">
+        <v>355</v>
+      </c>
       <c r="L7">
         <v>0.3</v>
       </c>
@@ -6331,7 +6493,10 @@
         <v>35</v>
       </c>
       <c r="J8" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+      <c r="K8" t="s">
+        <v>357</v>
       </c>
       <c r="L8">
         <v>0.05</v>
@@ -6369,7 +6534,10 @@
         <v>35</v>
       </c>
       <c r="J9" t="s">
-        <v>354</v>
+        <v>358</v>
+      </c>
+      <c r="K9" t="s">
+        <v>359</v>
       </c>
       <c r="L9">
         <v>7.0000000000000007E-2</v>
@@ -6413,7 +6581,10 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>354</v>
+        <v>360</v>
+      </c>
+      <c r="K10" t="s">
+        <v>361</v>
       </c>
       <c r="L10">
         <v>0.12</v>
@@ -6765,7 +6936,10 @@
         <v>68</v>
       </c>
       <c r="J18" t="s">
-        <v>354</v>
+        <v>362</v>
+      </c>
+      <c r="K18" t="s">
+        <v>363</v>
       </c>
       <c r="L18">
         <v>0.09</v>
@@ -6785,7 +6959,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B19" t="s">
         <v>69</v>
@@ -6803,7 +6977,10 @@
         <v>71</v>
       </c>
       <c r="J19" t="s">
-        <v>354</v>
+        <v>365</v>
+      </c>
+      <c r="K19" t="s">
+        <v>366</v>
       </c>
       <c r="L19">
         <v>4.4999999999999998E-2</v>
@@ -6846,6 +7023,9 @@
       <c r="J20" t="s">
         <v>354</v>
       </c>
+      <c r="K20" t="s">
+        <v>355</v>
+      </c>
       <c r="L20">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -6887,6 +7067,9 @@
       <c r="J21" t="s">
         <v>354</v>
       </c>
+      <c r="K21" t="s">
+        <v>355</v>
+      </c>
       <c r="L21">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -6926,7 +7109,10 @@
         <v>71</v>
       </c>
       <c r="J22" t="s">
-        <v>354</v>
+        <v>367</v>
+      </c>
+      <c r="K22" t="s">
+        <v>368</v>
       </c>
       <c r="L22">
         <v>0.1</v>
@@ -6969,6 +7155,9 @@
       <c r="J23" t="s">
         <v>354</v>
       </c>
+      <c r="K23" t="s">
+        <v>355</v>
+      </c>
       <c r="L23">
         <v>0.06</v>
       </c>
@@ -7010,6 +7199,9 @@
       <c r="J24" t="s">
         <v>354</v>
       </c>
+      <c r="K24" t="s">
+        <v>355</v>
+      </c>
       <c r="L24">
         <v>0.05</v>
       </c>
@@ -7049,7 +7241,10 @@
         <v>71</v>
       </c>
       <c r="J25" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+      <c r="K25" t="s">
+        <v>357</v>
       </c>
       <c r="L25">
         <v>0.05</v>
@@ -7090,7 +7285,10 @@
         <v>71</v>
       </c>
       <c r="J26" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+      <c r="K26" t="s">
+        <v>357</v>
       </c>
       <c r="L26">
         <v>0.1</v>
@@ -7131,7 +7329,10 @@
         <v>71</v>
       </c>
       <c r="J27" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+      <c r="K27" t="s">
+        <v>357</v>
       </c>
       <c r="L27">
         <v>0.1</v>
@@ -7171,6 +7372,9 @@
       <c r="J28" t="s">
         <v>354</v>
       </c>
+      <c r="K28" t="s">
+        <v>355</v>
+      </c>
       <c r="L28">
         <v>0.08</v>
       </c>
@@ -7207,7 +7411,10 @@
         <v>71</v>
       </c>
       <c r="J29" t="s">
-        <v>354</v>
+        <v>369</v>
+      </c>
+      <c r="K29" t="s">
+        <v>370</v>
       </c>
       <c r="L29">
         <v>3.5000000000000003E-2</v>
@@ -7245,7 +7452,10 @@
         <v>71</v>
       </c>
       <c r="J30" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="K30" t="s">
+        <v>372</v>
       </c>
       <c r="L30">
         <v>0.1</v>
@@ -7283,7 +7493,10 @@
         <v>71</v>
       </c>
       <c r="J31" t="s">
-        <v>354</v>
+        <v>373</v>
+      </c>
+      <c r="K31" t="s">
+        <v>374</v>
       </c>
       <c r="L31">
         <v>6.7000000000000004E-2</v>
@@ -7321,7 +7534,10 @@
         <v>71</v>
       </c>
       <c r="J32" t="s">
-        <v>354</v>
+        <v>375</v>
+      </c>
+      <c r="K32" t="s">
+        <v>376</v>
       </c>
       <c r="L32">
         <v>0.1</v>
@@ -7359,7 +7575,10 @@
         <v>71</v>
       </c>
       <c r="J33" t="s">
-        <v>354</v>
+        <v>367</v>
+      </c>
+      <c r="K33" t="s">
+        <v>368</v>
       </c>
       <c r="L33">
         <v>0.1</v>
@@ -7397,7 +7616,10 @@
         <v>71</v>
       </c>
       <c r="J34" t="s">
-        <v>354</v>
+        <v>369</v>
+      </c>
+      <c r="K34" t="s">
+        <v>370</v>
       </c>
       <c r="L34">
         <v>0.105</v>
@@ -7435,7 +7657,10 @@
         <v>71</v>
       </c>
       <c r="J35" t="s">
-        <v>354</v>
+        <v>358</v>
+      </c>
+      <c r="K35" t="s">
+        <v>359</v>
       </c>
       <c r="L35">
         <v>7.0000000000000007E-2</v>
@@ -7476,7 +7701,10 @@
         <v>71</v>
       </c>
       <c r="J36" t="s">
-        <v>354</v>
+        <v>377</v>
+      </c>
+      <c r="K36" t="s">
+        <v>378</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -7517,7 +7745,10 @@
         <v>71</v>
       </c>
       <c r="J37" t="s">
-        <v>354</v>
+        <v>379</v>
+      </c>
+      <c r="K37" t="s">
+        <v>380</v>
       </c>
       <c r="L37">
         <v>0.09</v>
@@ -7555,7 +7786,10 @@
         <v>71</v>
       </c>
       <c r="J38" t="s">
-        <v>354</v>
+        <v>381</v>
+      </c>
+      <c r="K38" t="s">
+        <v>382</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -7593,7 +7827,10 @@
         <v>71</v>
       </c>
       <c r="J39" t="s">
-        <v>354</v>
+        <v>381</v>
+      </c>
+      <c r="K39" t="s">
+        <v>382</v>
       </c>
       <c r="L39">
         <v>3</v>
@@ -7921,7 +8158,7 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="B47" t="s">
         <v>128</v>
@@ -7939,7 +8176,10 @@
         <v>129</v>
       </c>
       <c r="J47" t="s">
-        <v>354</v>
+        <v>384</v>
+      </c>
+      <c r="K47" t="s">
+        <v>385</v>
       </c>
       <c r="L47">
         <v>3.4000000000000002E-2</v>
@@ -7983,10 +8223,10 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s">
-        <v>358</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
         <v>70</v>
@@ -8001,22 +8241,25 @@
         <v>129</v>
       </c>
       <c r="J48" t="s">
-        <v>354</v>
+        <v>384</v>
+      </c>
+      <c r="K48" t="s">
+        <v>385</v>
       </c>
       <c r="L48">
-        <v>6.4704000000000012E-2</v>
+        <v>2.7847291139240511E-2</v>
       </c>
       <c r="M48">
-        <v>3421.2499999999995</v>
+        <v>4016.25</v>
       </c>
       <c r="N48">
-        <v>128.70000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="O48">
-        <v>7.9200000000000017</v>
+        <v>8.64</v>
       </c>
       <c r="P48">
-        <v>0.23760000000000003</v>
+        <v>0.23040000000000005</v>
       </c>
       <c r="R48">
         <v>38</v>
@@ -8043,45 +8286,72 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s">
         <v>128</v>
       </c>
       <c r="C49" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
       </c>
       <c r="E49">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="I49" t="s">
         <v>129</v>
       </c>
       <c r="J49" t="s">
-        <v>354</v>
+        <v>365</v>
+      </c>
+      <c r="K49" t="s">
+        <v>366</v>
       </c>
       <c r="L49">
-        <v>2.5000000000000001E-3</v>
+        <v>3.6856708860759493E-2</v>
       </c>
       <c r="M49">
-        <v>4819.5</v>
+        <v>4016.25</v>
       </c>
       <c r="N49">
         <v>152.1</v>
       </c>
       <c r="O49">
-        <v>2.7</v>
+        <v>8.64</v>
       </c>
       <c r="P49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
+        <v>0.23040000000000008</v>
+      </c>
+      <c r="R49">
+        <v>38</v>
+      </c>
+      <c r="S49">
+        <v>5</v>
+      </c>
+      <c r="T49">
+        <v>5</v>
+      </c>
+      <c r="U49">
+        <v>30</v>
+      </c>
+      <c r="V49">
+        <v>30</v>
+      </c>
+      <c r="W49">
+        <v>5</v>
+      </c>
+      <c r="X49">
+        <v>40</v>
+      </c>
+      <c r="Y49">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>130</v>
       </c>
@@ -8106,6 +8376,9 @@
       <c r="J50" t="s">
         <v>354</v>
       </c>
+      <c r="K50" t="s">
+        <v>355</v>
+      </c>
       <c r="L50">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -8122,7 +8395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>133</v>
       </c>
@@ -8147,6 +8420,9 @@
       <c r="J51" t="s">
         <v>354</v>
       </c>
+      <c r="K51" t="s">
+        <v>355</v>
+      </c>
       <c r="L51">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -8163,7 +8439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>135</v>
       </c>
@@ -8188,6 +8464,9 @@
       <c r="J52" t="s">
         <v>354</v>
       </c>
+      <c r="K52" t="s">
+        <v>355</v>
+      </c>
       <c r="L52">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -8204,7 +8483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>137</v>
       </c>
@@ -8227,7 +8506,10 @@
         <v>129</v>
       </c>
       <c r="J53" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K53" t="s">
+        <v>389</v>
       </c>
       <c r="L53">
         <v>7.0000000000000007E-2</v>
@@ -8245,7 +8527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>139</v>
       </c>
@@ -8268,7 +8550,10 @@
         <v>129</v>
       </c>
       <c r="J54" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K54" t="s">
+        <v>389</v>
       </c>
       <c r="L54">
         <v>7.0000000000000007E-2</v>
@@ -8286,7 +8571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>141</v>
       </c>
@@ -8309,7 +8594,10 @@
         <v>129</v>
       </c>
       <c r="J55" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K55" t="s">
+        <v>389</v>
       </c>
       <c r="L55">
         <v>8.3000000000000004E-2</v>
@@ -8327,7 +8615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>143</v>
       </c>
@@ -8352,6 +8640,9 @@
       <c r="J56" t="s">
         <v>354</v>
       </c>
+      <c r="K56" t="s">
+        <v>355</v>
+      </c>
       <c r="L56">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -8368,7 +8659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>145</v>
       </c>
@@ -8393,6 +8684,9 @@
       <c r="J57" t="s">
         <v>354</v>
       </c>
+      <c r="K57" t="s">
+        <v>355</v>
+      </c>
       <c r="L57">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -8409,7 +8703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>147</v>
       </c>
@@ -8434,6 +8728,9 @@
       <c r="J58" t="s">
         <v>354</v>
       </c>
+      <c r="K58" t="s">
+        <v>355</v>
+      </c>
       <c r="L58">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -8450,7 +8747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>149</v>
       </c>
@@ -8473,7 +8770,10 @@
         <v>129</v>
       </c>
       <c r="J59" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K59" t="s">
+        <v>389</v>
       </c>
       <c r="L59">
         <v>5.8999999999999997E-2</v>
@@ -8491,7 +8791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>151</v>
       </c>
@@ -8514,7 +8814,10 @@
         <v>129</v>
       </c>
       <c r="J60" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K60" t="s">
+        <v>389</v>
       </c>
       <c r="L60">
         <v>3.5999999999999997E-2</v>
@@ -8532,7 +8835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>153</v>
       </c>
@@ -8555,7 +8858,10 @@
         <v>129</v>
       </c>
       <c r="J61" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="K61" t="s">
+        <v>372</v>
       </c>
       <c r="L61">
         <v>7.0000000000000007E-2</v>
@@ -8573,7 +8879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>155</v>
       </c>
@@ -8596,7 +8902,10 @@
         <v>129</v>
       </c>
       <c r="J62" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="K62" t="s">
+        <v>372</v>
       </c>
       <c r="L62">
         <v>7.0000000000000007E-2</v>
@@ -8614,7 +8923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>157</v>
       </c>
@@ -8637,7 +8946,10 @@
         <v>129</v>
       </c>
       <c r="J63" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="K63" t="s">
+        <v>372</v>
       </c>
       <c r="L63">
         <v>8.2000000000000003E-2</v>
@@ -8655,7 +8967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>159</v>
       </c>
@@ -8678,7 +8990,10 @@
         <v>129</v>
       </c>
       <c r="J64" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="K64" t="s">
+        <v>372</v>
       </c>
       <c r="L64">
         <v>8.2000000000000003E-2</v>
@@ -8722,7 +9037,10 @@
         <v>129</v>
       </c>
       <c r="J65" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K65" t="s">
+        <v>389</v>
       </c>
       <c r="L65">
         <v>1.4999999999999999E-2</v>
@@ -8766,7 +9084,10 @@
         <v>129</v>
       </c>
       <c r="J66" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K66" t="s">
+        <v>389</v>
       </c>
       <c r="L66">
         <v>1.4999999999999999E-2</v>
@@ -8810,7 +9131,10 @@
         <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K67" t="s">
+        <v>389</v>
       </c>
       <c r="L67">
         <v>1.4999999999999999E-2</v>
@@ -8851,7 +9175,10 @@
         <v>132</v>
       </c>
       <c r="J68" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K68" t="s">
+        <v>389</v>
       </c>
       <c r="L68">
         <v>2.1000000000000001E-2</v>
@@ -8892,7 +9219,10 @@
         <v>132</v>
       </c>
       <c r="J69" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K69" t="s">
+        <v>389</v>
       </c>
       <c r="L69">
         <v>2.1000000000000001E-2</v>
@@ -8933,7 +9263,10 @@
         <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K70" t="s">
+        <v>389</v>
       </c>
       <c r="L70">
         <v>2.1000000000000001E-2</v>
@@ -8974,7 +9307,10 @@
         <v>129</v>
       </c>
       <c r="J71" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K71" t="s">
+        <v>389</v>
       </c>
       <c r="L71">
         <v>2.5999999999999999E-2</v>
@@ -9015,7 +9351,10 @@
         <v>129</v>
       </c>
       <c r="J72" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K72" t="s">
+        <v>389</v>
       </c>
       <c r="L72">
         <v>2.5999999999999999E-2</v>
@@ -9055,6 +9394,9 @@
       <c r="J73" t="s">
         <v>354</v>
       </c>
+      <c r="K73" t="s">
+        <v>355</v>
+      </c>
       <c r="L73">
         <v>3.5000000000000003E-2</v>
       </c>
@@ -9073,10 +9415,10 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="B74" t="s">
-        <v>361</v>
+        <v>391</v>
       </c>
       <c r="C74" t="s">
         <v>33</v>
@@ -9091,19 +9433,22 @@
         <v>129</v>
       </c>
       <c r="J74" t="s">
-        <v>354</v>
+        <v>388</v>
+      </c>
+      <c r="K74" t="s">
+        <v>389</v>
       </c>
       <c r="L74">
-        <v>0.12322999999999995</v>
+        <v>2.1763879549233318E-2</v>
       </c>
       <c r="M74">
-        <v>4105.5</v>
+        <v>4819.5</v>
       </c>
       <c r="N74">
-        <v>128.70000000000002</v>
+        <v>152.1</v>
       </c>
       <c r="O74">
-        <v>2.4749999999999996</v>
+        <v>2.7</v>
       </c>
       <c r="P74">
         <v>1</v>
@@ -9111,19 +9456,19 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>362</v>
+        <v>392</v>
       </c>
       <c r="B75" t="s">
-        <v>363</v>
+        <v>128</v>
       </c>
       <c r="C75" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D75" t="s">
         <v>3</v>
       </c>
       <c r="E75">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="I75" t="s">
         <v>129</v>
@@ -9131,31 +9476,40 @@
       <c r="J75" t="s">
         <v>354</v>
       </c>
+      <c r="K75" t="s">
+        <v>355</v>
+      </c>
       <c r="L75">
-        <v>0.13633100000000009</v>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="M75">
+        <v>4819.5</v>
+      </c>
+      <c r="N75">
+        <v>152.1</v>
+      </c>
+      <c r="O75">
+        <v>2.7</v>
       </c>
       <c r="P75">
-        <v>0.33123000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>179</v>
+        <v>393</v>
       </c>
       <c r="B76" t="s">
-        <v>180</v>
+        <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D76" t="s">
         <v>3</v>
       </c>
       <c r="E76">
-        <v>1974</v>
-      </c>
-      <c r="G76" t="s">
-        <v>181</v>
+        <v>2022</v>
       </c>
       <c r="I76" t="s">
         <v>129</v>
@@ -9163,17 +9517,20 @@
       <c r="J76" t="s">
         <v>354</v>
       </c>
+      <c r="K76" t="s">
+        <v>355</v>
+      </c>
       <c r="L76">
-        <v>9.4E-2</v>
+        <v>6.941220580084978E-2</v>
       </c>
       <c r="M76">
-        <v>2443.75</v>
+        <v>4105.5</v>
       </c>
       <c r="N76">
-        <v>49.500000000000007</v>
+        <v>128.70000000000002</v>
       </c>
       <c r="O76">
-        <v>1.9800000000000004</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="P76">
         <v>1</v>
@@ -9181,40 +9538,40 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>182</v>
+        <v>395</v>
       </c>
       <c r="B77" t="s">
-        <v>183</v>
+        <v>396</v>
       </c>
       <c r="C77" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D77" t="s">
         <v>3</v>
       </c>
       <c r="E77">
-        <v>1988</v>
-      </c>
-      <c r="G77" t="s">
-        <v>108</v>
+        <v>2022</v>
       </c>
       <c r="I77" t="s">
         <v>129</v>
       </c>
       <c r="J77" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+      <c r="K77" t="s">
+        <v>357</v>
       </c>
       <c r="L77">
-        <v>0.16800000000000001</v>
+        <v>1.3659338629225932E-2</v>
       </c>
       <c r="M77">
-        <v>2443.75</v>
+        <v>4819.5</v>
       </c>
       <c r="N77">
-        <v>49.500000000000014</v>
+        <v>152.1</v>
       </c>
       <c r="O77">
-        <v>1.9800000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="P77">
         <v>1</v>
@@ -9222,40 +9579,40 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>184</v>
+        <v>397</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>398</v>
       </c>
       <c r="C78" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D78" t="s">
         <v>3</v>
       </c>
       <c r="E78">
-        <v>1991</v>
-      </c>
-      <c r="G78" t="s">
-        <v>186</v>
+        <v>2022</v>
       </c>
       <c r="I78" t="s">
         <v>129</v>
       </c>
       <c r="J78" t="s">
-        <v>354</v>
+        <v>371</v>
+      </c>
+      <c r="K78" t="s">
+        <v>372</v>
       </c>
       <c r="L78">
-        <v>0.10299999999999999</v>
+        <v>1.839457602069092E-2</v>
       </c>
       <c r="M78">
-        <v>2443.75</v>
+        <v>4819.5</v>
       </c>
       <c r="N78">
-        <v>49.500000000000007</v>
+        <v>152.1</v>
       </c>
       <c r="O78">
-        <v>1.9800000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="P78">
         <v>1</v>
@@ -9263,10 +9620,10 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>187</v>
+        <v>399</v>
       </c>
       <c r="B79" t="s">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="C79" t="s">
         <v>43</v>
@@ -9275,39 +9632,30 @@
         <v>3</v>
       </c>
       <c r="E79">
-        <v>2013</v>
-      </c>
-      <c r="G79" t="s">
-        <v>111</v>
+        <v>2022</v>
       </c>
       <c r="I79" t="s">
         <v>129</v>
       </c>
       <c r="J79" t="s">
-        <v>354</v>
+        <v>379</v>
+      </c>
+      <c r="K79" t="s">
+        <v>380</v>
       </c>
       <c r="L79">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="M79">
-        <v>2443.75</v>
-      </c>
-      <c r="N79">
-        <v>49.500000000000007</v>
-      </c>
-      <c r="O79">
-        <v>1.98</v>
+        <v>2.5341064841498579E-2</v>
       </c>
       <c r="P79">
-        <v>1</v>
+        <v>0.33123000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
         <v>43</v>
@@ -9316,7 +9664,7 @@
         <v>3</v>
       </c>
       <c r="E80">
-        <v>1978</v>
+        <v>1974</v>
       </c>
       <c r="G80" t="s">
         <v>181</v>
@@ -9325,19 +9673,22 @@
         <v>129</v>
       </c>
       <c r="J80" t="s">
-        <v>354</v>
+        <v>401</v>
+      </c>
+      <c r="K80" t="s">
+        <v>402</v>
       </c>
       <c r="L80">
-        <v>0.22500000000000001</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M80">
-        <v>2150.5</v>
+        <v>2443.75</v>
       </c>
       <c r="N80">
-        <v>54.45000000000001</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="O80">
-        <v>2.4750000000000001</v>
+        <v>1.9800000000000004</v>
       </c>
       <c r="P80">
         <v>1</v>
@@ -9345,10 +9696,10 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B81" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s">
         <v>43</v>
@@ -9357,31 +9708,31 @@
         <v>3</v>
       </c>
       <c r="E81">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="G81" t="s">
-        <v>193</v>
-      </c>
-      <c r="H81" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="I81" t="s">
         <v>129</v>
       </c>
       <c r="J81" t="s">
-        <v>354</v>
+        <v>377</v>
+      </c>
+      <c r="K81" t="s">
+        <v>378</v>
       </c>
       <c r="L81">
-        <v>0.06</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="M81">
-        <v>2150.5</v>
+        <v>2443.75</v>
       </c>
       <c r="N81">
-        <v>54.45000000000001</v>
+        <v>49.500000000000014</v>
       </c>
       <c r="O81">
-        <v>2.4750000000000001</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="P81">
         <v>1</v>
@@ -9389,10 +9740,10 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B82" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
         <v>43</v>
@@ -9401,25 +9752,31 @@
         <v>3</v>
       </c>
       <c r="E82">
-        <v>2028</v>
+        <v>1991</v>
+      </c>
+      <c r="G82" t="s">
+        <v>186</v>
       </c>
       <c r="I82" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J82" t="s">
-        <v>354</v>
+        <v>358</v>
+      </c>
+      <c r="K82" t="s">
+        <v>359</v>
       </c>
       <c r="L82">
-        <v>0.06</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="M82">
-        <v>2150.5</v>
+        <v>2443.75</v>
       </c>
       <c r="N82">
-        <v>54.45000000000001</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="O82">
-        <v>2.4750000000000001</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="P82">
         <v>1</v>
@@ -9427,13 +9784,13 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B83" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C83" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
         <v>3</v>
@@ -9441,410 +9798,236 @@
       <c r="E83">
         <v>2013</v>
       </c>
-      <c r="F83">
-        <v>2034</v>
-      </c>
       <c r="G83" t="s">
-        <v>200</v>
-      </c>
-      <c r="H83" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="I83" t="s">
         <v>129</v>
       </c>
       <c r="J83" t="s">
-        <v>354</v>
+        <v>379</v>
+      </c>
+      <c r="K83" t="s">
+        <v>380</v>
       </c>
       <c r="L83">
-        <v>8.6999999999999994E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="M83">
-        <v>977.5</v>
+        <v>2443.75</v>
       </c>
       <c r="N83">
-        <v>39.6</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="O83">
-        <v>6.4350000000000005</v>
+        <v>1.98</v>
       </c>
       <c r="P83">
-        <v>0.252</v>
-      </c>
-      <c r="R83">
-        <v>35</v>
-      </c>
-      <c r="S83">
-        <v>2</v>
-      </c>
-      <c r="T83">
-        <v>2</v>
-      </c>
-      <c r="U83">
-        <v>60</v>
-      </c>
-      <c r="V83">
-        <v>60</v>
-      </c>
-      <c r="W83">
-        <v>1.5</v>
-      </c>
-      <c r="X83">
-        <v>20</v>
-      </c>
-      <c r="Y83">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B84" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C84" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
         <v>3</v>
       </c>
       <c r="E84">
-        <v>2009</v>
-      </c>
-      <c r="F84">
-        <v>2030</v>
-      </c>
-      <c r="H84" t="s">
-        <v>204</v>
+        <v>1978</v>
+      </c>
+      <c r="G84" t="s">
+        <v>181</v>
       </c>
       <c r="I84" t="s">
         <v>129</v>
       </c>
       <c r="J84" t="s">
-        <v>354</v>
+        <v>379</v>
+      </c>
+      <c r="K84" t="s">
+        <v>380</v>
       </c>
       <c r="L84">
-        <v>8.5000000000000006E-2</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="M84">
-        <v>977.5</v>
+        <v>2150.5</v>
       </c>
       <c r="N84">
-        <v>39.6</v>
+        <v>54.45000000000001</v>
       </c>
       <c r="O84">
-        <v>6.4350000000000005</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="P84">
-        <v>0.24480000000000005</v>
-      </c>
-      <c r="R84">
-        <v>35</v>
-      </c>
-      <c r="S84">
-        <v>2</v>
-      </c>
-      <c r="T84">
-        <v>2</v>
-      </c>
-      <c r="U84">
-        <v>60</v>
-      </c>
-      <c r="V84">
-        <v>60</v>
-      </c>
-      <c r="W84">
-        <v>1.5</v>
-      </c>
-      <c r="X84">
-        <v>20</v>
-      </c>
-      <c r="Y84">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
         <v>3</v>
       </c>
       <c r="E85">
-        <v>1987</v>
+        <v>2008</v>
+      </c>
+      <c r="G85" t="s">
+        <v>193</v>
       </c>
       <c r="H85" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="I85" t="s">
         <v>129</v>
       </c>
       <c r="J85" t="s">
-        <v>354</v>
+        <v>360</v>
+      </c>
+      <c r="K85" t="s">
+        <v>361</v>
       </c>
       <c r="L85">
         <v>0.06</v>
       </c>
       <c r="M85">
-        <v>977.5</v>
+        <v>2150.5</v>
       </c>
       <c r="N85">
-        <v>39.6</v>
+        <v>54.45000000000001</v>
       </c>
       <c r="O85">
-        <v>6.4350000000000005</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="P85">
-        <v>0.22680000000000003</v>
-      </c>
-      <c r="R85">
-        <v>35</v>
-      </c>
-      <c r="S85">
-        <v>2</v>
-      </c>
-      <c r="T85">
-        <v>2</v>
-      </c>
-      <c r="U85">
-        <v>60</v>
-      </c>
-      <c r="V85">
-        <v>60</v>
-      </c>
-      <c r="W85">
-        <v>1.5</v>
-      </c>
-      <c r="X85">
-        <v>20</v>
-      </c>
-      <c r="Y85">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B86" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C86" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D86" t="s">
         <v>3</v>
       </c>
       <c r="E86">
-        <v>2010</v>
-      </c>
-      <c r="F86">
-        <v>2031</v>
-      </c>
-      <c r="G86" t="s">
-        <v>210</v>
-      </c>
-      <c r="H86" t="s">
-        <v>210</v>
+        <v>2028</v>
       </c>
       <c r="I86" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J86" t="s">
-        <v>354</v>
+        <v>367</v>
+      </c>
+      <c r="K86" t="s">
+        <v>368</v>
       </c>
       <c r="L86">
-        <v>0.1169</v>
+        <v>0.06</v>
       </c>
       <c r="M86">
-        <v>977.5</v>
+        <v>2150.5</v>
       </c>
       <c r="N86">
-        <v>39.6</v>
+        <v>54.45000000000001</v>
       </c>
       <c r="O86">
-        <v>6.4350000000000005</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="P86">
-        <v>0.24480000000000005</v>
-      </c>
-      <c r="R86">
-        <v>35</v>
-      </c>
-      <c r="S86">
-        <v>2</v>
-      </c>
-      <c r="T86">
-        <v>2</v>
-      </c>
-      <c r="U86">
-        <v>60</v>
-      </c>
-      <c r="V86">
-        <v>60</v>
-      </c>
-      <c r="W86">
-        <v>1.5</v>
-      </c>
-      <c r="X86">
-        <v>20</v>
-      </c>
-      <c r="Y86">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>211</v>
+        <v>403</v>
       </c>
       <c r="B87" t="s">
-        <v>212</v>
+        <v>404</v>
       </c>
       <c r="C87" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D87" t="s">
         <v>3</v>
       </c>
       <c r="E87">
-        <v>1999</v>
-      </c>
-      <c r="F87">
-        <v>2023</v>
-      </c>
-      <c r="G87" t="s">
-        <v>210</v>
-      </c>
-      <c r="H87" t="s">
-        <v>210</v>
+        <v>2022</v>
       </c>
       <c r="I87" t="s">
         <v>129</v>
       </c>
       <c r="J87" t="s">
-        <v>354</v>
+        <v>360</v>
+      </c>
+      <c r="K87" t="s">
+        <v>361</v>
       </c>
       <c r="L87">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="M87">
-        <v>977.5</v>
-      </c>
-      <c r="N87">
-        <v>39.6</v>
-      </c>
-      <c r="O87">
-        <v>6.4350000000000005</v>
+        <v>1.1786541786743524E-2</v>
       </c>
       <c r="P87">
-        <v>0.23400000000000004</v>
-      </c>
-      <c r="R87">
-        <v>35</v>
-      </c>
-      <c r="S87">
-        <v>2</v>
-      </c>
-      <c r="T87">
-        <v>2</v>
-      </c>
-      <c r="U87">
-        <v>60</v>
-      </c>
-      <c r="V87">
-        <v>60</v>
-      </c>
-      <c r="W87">
-        <v>1.5</v>
-      </c>
-      <c r="X87">
-        <v>20</v>
-      </c>
-      <c r="Y87">
-        <v>6</v>
+        <v>0.33123000000000002</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>405</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>199</v>
+        <v>43</v>
       </c>
       <c r="D88" t="s">
         <v>3</v>
       </c>
       <c r="E88">
-        <v>2004</v>
-      </c>
-      <c r="F88">
-        <v>2034</v>
-      </c>
-      <c r="H88" t="s">
-        <v>215</v>
+        <v>2022</v>
       </c>
       <c r="I88" t="s">
         <v>129</v>
       </c>
       <c r="J88" t="s">
-        <v>354</v>
+        <v>377</v>
+      </c>
+      <c r="K88" t="s">
+        <v>378</v>
       </c>
       <c r="L88">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M88">
-        <v>977.5</v>
-      </c>
-      <c r="N88">
-        <v>39.6</v>
-      </c>
-      <c r="O88">
-        <v>6.4350000000000005</v>
+        <v>9.9203393371757986E-2</v>
       </c>
       <c r="P88">
-        <v>0.24480000000000005</v>
-      </c>
-      <c r="R88">
-        <v>35</v>
-      </c>
-      <c r="S88">
-        <v>2</v>
-      </c>
-      <c r="T88">
-        <v>2</v>
-      </c>
-      <c r="U88">
-        <v>60</v>
-      </c>
-      <c r="V88">
-        <v>60</v>
-      </c>
-      <c r="W88">
-        <v>1.5</v>
-      </c>
-      <c r="X88">
-        <v>20</v>
-      </c>
-      <c r="Y88">
-        <v>6</v>
+        <v>0.33122999999999997</v>
       </c>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
         <v>199</v>
@@ -9853,22 +10036,28 @@
         <v>3</v>
       </c>
       <c r="E89">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F89">
-        <v>2035</v>
+        <v>2034</v>
+      </c>
+      <c r="G89" t="s">
+        <v>200</v>
       </c>
       <c r="H89" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="I89" t="s">
         <v>129</v>
       </c>
       <c r="J89" t="s">
-        <v>354</v>
+        <v>407</v>
+      </c>
+      <c r="K89" t="s">
+        <v>408</v>
       </c>
       <c r="L89">
-        <v>8.3199999999999996E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="M89">
         <v>977.5</v>
@@ -9909,10 +10098,10 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
         <v>199</v>
@@ -9921,22 +10110,25 @@
         <v>3</v>
       </c>
       <c r="E90">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="F90">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="H90" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="I90" t="s">
         <v>129</v>
       </c>
       <c r="J90" t="s">
-        <v>354</v>
+        <v>409</v>
+      </c>
+      <c r="K90" t="s">
+        <v>410</v>
       </c>
       <c r="L90">
-        <v>0.08</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="M90">
         <v>977.5</v>
@@ -9948,7 +10140,7 @@
         <v>6.4350000000000005</v>
       </c>
       <c r="P90">
-        <v>0.252</v>
+        <v>0.24480000000000005</v>
       </c>
       <c r="R90">
         <v>35</v>
@@ -9977,162 +10169,300 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="C91" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="D91" t="s">
         <v>3</v>
       </c>
       <c r="E91">
-        <v>2022</v>
+        <v>1987</v>
+      </c>
+      <c r="H91" t="s">
+        <v>207</v>
       </c>
       <c r="I91" t="s">
         <v>129</v>
       </c>
       <c r="J91" t="s">
-        <v>222</v>
-      </c>
-      <c r="K91">
-        <v>4</v>
+        <v>360</v>
+      </c>
+      <c r="K91" t="s">
+        <v>361</v>
       </c>
       <c r="L91">
-        <v>2.2195369641804075E-2</v>
+        <v>0.06</v>
+      </c>
+      <c r="M91">
+        <v>977.5</v>
+      </c>
+      <c r="N91">
+        <v>39.6</v>
+      </c>
+      <c r="O91">
+        <v>6.4350000000000005</v>
       </c>
       <c r="P91">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="Q91">
-        <v>0.23864191972779222</v>
+        <v>0.22680000000000003</v>
+      </c>
+      <c r="R91">
+        <v>35</v>
+      </c>
+      <c r="S91">
+        <v>2</v>
+      </c>
+      <c r="T91">
+        <v>2</v>
+      </c>
+      <c r="U91">
+        <v>60</v>
+      </c>
+      <c r="V91">
+        <v>60</v>
+      </c>
+      <c r="W91">
+        <v>1.5</v>
+      </c>
+      <c r="X91">
+        <v>20</v>
+      </c>
+      <c r="Y91">
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="C92" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="D92" t="s">
         <v>3</v>
       </c>
       <c r="E92">
-        <v>2022</v>
+        <v>2010</v>
+      </c>
+      <c r="F92">
+        <v>2031</v>
+      </c>
+      <c r="G92" t="s">
+        <v>210</v>
+      </c>
+      <c r="H92" t="s">
+        <v>210</v>
       </c>
       <c r="I92" t="s">
         <v>129</v>
       </c>
       <c r="J92" t="s">
-        <v>224</v>
-      </c>
-      <c r="K92">
-        <v>16</v>
+        <v>411</v>
+      </c>
+      <c r="K92" t="s">
+        <v>412</v>
       </c>
       <c r="L92">
-        <v>1.9490684055002715E-2</v>
+        <v>0.1169</v>
+      </c>
+      <c r="M92">
+        <v>977.5</v>
+      </c>
+      <c r="N92">
+        <v>39.6</v>
+      </c>
+      <c r="O92">
+        <v>6.4350000000000005</v>
       </c>
       <c r="P92">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="Q92">
-        <v>0.23864191972779222</v>
+        <v>0.24480000000000005</v>
+      </c>
+      <c r="R92">
+        <v>35</v>
+      </c>
+      <c r="S92">
+        <v>2</v>
+      </c>
+      <c r="T92">
+        <v>2</v>
+      </c>
+      <c r="U92">
+        <v>60</v>
+      </c>
+      <c r="V92">
+        <v>60</v>
+      </c>
+      <c r="W92">
+        <v>1.5</v>
+      </c>
+      <c r="X92">
+        <v>20</v>
+      </c>
+      <c r="Y92">
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="B93" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="C93" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="D93" t="s">
         <v>3</v>
       </c>
       <c r="E93">
-        <v>2022</v>
+        <v>1999</v>
+      </c>
+      <c r="F93">
+        <v>2023</v>
+      </c>
+      <c r="G93" t="s">
+        <v>210</v>
+      </c>
+      <c r="H93" t="s">
+        <v>210</v>
       </c>
       <c r="I93" t="s">
         <v>129</v>
       </c>
       <c r="J93" t="s">
-        <v>51</v>
-      </c>
-      <c r="K93">
-        <v>22</v>
+        <v>411</v>
+      </c>
+      <c r="K93" t="s">
+        <v>412</v>
       </c>
       <c r="L93">
-        <v>1.9760946303193187E-2</v>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="M93">
+        <v>977.5</v>
+      </c>
+      <c r="N93">
+        <v>39.6</v>
+      </c>
+      <c r="O93">
+        <v>6.4350000000000005</v>
       </c>
       <c r="P93">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="Q93">
-        <v>0.23864191972779222</v>
+        <v>0.23400000000000004</v>
+      </c>
+      <c r="R93">
+        <v>35</v>
+      </c>
+      <c r="S93">
+        <v>2</v>
+      </c>
+      <c r="T93">
+        <v>2</v>
+      </c>
+      <c r="U93">
+        <v>60</v>
+      </c>
+      <c r="V93">
+        <v>60</v>
+      </c>
+      <c r="W93">
+        <v>1.5</v>
+      </c>
+      <c r="X93">
+        <v>20</v>
+      </c>
+      <c r="Y93">
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C94" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="D94" t="s">
         <v>3</v>
       </c>
       <c r="E94">
-        <v>2028</v>
+        <v>2004</v>
+      </c>
+      <c r="F94">
+        <v>2034</v>
+      </c>
+      <c r="H94" t="s">
+        <v>215</v>
       </c>
       <c r="I94" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J94" t="s">
-        <v>118</v>
-      </c>
-      <c r="K94">
-        <v>7</v>
+        <v>413</v>
+      </c>
+      <c r="K94" t="s">
+        <v>414</v>
       </c>
       <c r="L94">
-        <v>0.04</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="M94">
-        <v>1032.75</v>
+        <v>977.5</v>
       </c>
       <c r="N94">
-        <v>17.55</v>
+        <v>39.6</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>6.4350000000000005</v>
       </c>
       <c r="P94">
-        <v>1</v>
-      </c>
-      <c r="Q94">
-        <v>0.2301224015067071</v>
+        <v>0.24480000000000005</v>
+      </c>
+      <c r="R94">
+        <v>35</v>
+      </c>
+      <c r="S94">
+        <v>2</v>
+      </c>
+      <c r="T94">
+        <v>2</v>
+      </c>
+      <c r="U94">
+        <v>60</v>
+      </c>
+      <c r="V94">
+        <v>60</v>
+      </c>
+      <c r="W94">
+        <v>1.5</v>
+      </c>
+      <c r="X94">
+        <v>20</v>
+      </c>
+      <c r="Y94">
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B95" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="C95" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="D95" t="s">
         <v>3</v>
@@ -10140,81 +10470,135 @@
       <c r="E95">
         <v>2015</v>
       </c>
+      <c r="F95">
+        <v>2035</v>
+      </c>
+      <c r="H95" t="s">
+        <v>218</v>
+      </c>
       <c r="I95" t="s">
         <v>129</v>
       </c>
       <c r="J95" t="s">
-        <v>229</v>
-      </c>
-      <c r="K95">
-        <v>9</v>
+        <v>415</v>
+      </c>
+      <c r="K95" t="s">
+        <v>416</v>
       </c>
       <c r="L95">
-        <v>0.04</v>
+        <v>8.3199999999999996E-2</v>
       </c>
       <c r="M95">
-        <v>1032.75</v>
+        <v>977.5</v>
       </c>
       <c r="N95">
-        <v>17.55</v>
+        <v>39.6</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>6.4350000000000005</v>
       </c>
       <c r="P95">
-        <v>1</v>
-      </c>
-      <c r="Q95">
-        <v>0.25369869095953879</v>
+        <v>0.252</v>
+      </c>
+      <c r="R95">
+        <v>35</v>
+      </c>
+      <c r="S95">
+        <v>2</v>
+      </c>
+      <c r="T95">
+        <v>2</v>
+      </c>
+      <c r="U95">
+        <v>60</v>
+      </c>
+      <c r="V95">
+        <v>60</v>
+      </c>
+      <c r="W95">
+        <v>1.5</v>
+      </c>
+      <c r="X95">
+        <v>20</v>
+      </c>
+      <c r="Y95">
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B96" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="C96" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="D96" t="s">
         <v>3</v>
       </c>
       <c r="E96">
-        <v>2021</v>
+        <v>2014</v>
+      </c>
+      <c r="F96">
+        <v>2034</v>
+      </c>
+      <c r="H96" t="s">
+        <v>218</v>
       </c>
       <c r="I96" t="s">
         <v>129</v>
       </c>
       <c r="J96" t="s">
-        <v>229</v>
-      </c>
-      <c r="K96">
-        <v>9</v>
+        <v>415</v>
+      </c>
+      <c r="K96" t="s">
+        <v>416</v>
       </c>
       <c r="L96">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="M96">
-        <v>1032.75</v>
+        <v>977.5</v>
       </c>
       <c r="N96">
-        <v>17.55</v>
+        <v>39.6</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>6.4350000000000005</v>
       </c>
       <c r="P96">
-        <v>1</v>
-      </c>
-      <c r="Q96">
-        <v>0.25369869095953879</v>
+        <v>0.252</v>
+      </c>
+      <c r="R96">
+        <v>35</v>
+      </c>
+      <c r="S96">
+        <v>2</v>
+      </c>
+      <c r="T96">
+        <v>2</v>
+      </c>
+      <c r="U96">
+        <v>60</v>
+      </c>
+      <c r="V96">
+        <v>60</v>
+      </c>
+      <c r="W96">
+        <v>1.5</v>
+      </c>
+      <c r="X96">
+        <v>20</v>
+      </c>
+      <c r="Y96">
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B97" t="s">
         <v>128</v>
@@ -10232,33 +10616,24 @@
         <v>129</v>
       </c>
       <c r="J97" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="K97">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L97">
-        <v>0.04</v>
-      </c>
-      <c r="M97">
-        <v>1032.75</v>
-      </c>
-      <c r="N97">
-        <v>17.55</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
+        <v>2.2195369641804075E-2</v>
       </c>
       <c r="P97">
-        <v>1</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="Q97">
-        <v>0.25369869095953879</v>
+        <v>0.2386419197277922</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
@@ -10270,42 +10645,33 @@
         <v>3</v>
       </c>
       <c r="E98">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I98" t="s">
         <v>129</v>
       </c>
       <c r="J98" t="s">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="K98">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L98">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="M98">
-        <v>1032.75</v>
-      </c>
-      <c r="N98">
-        <v>17.55</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
+        <v>1.9490684055002715E-2</v>
       </c>
       <c r="P98">
-        <v>1</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="Q98">
-        <v>0.23354545132238791</v>
+        <v>0.2386419197277922</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B99" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="C99" t="s">
         <v>48</v>
@@ -10314,42 +10680,33 @@
         <v>3</v>
       </c>
       <c r="E99">
-        <v>2028</v>
+        <v>2022</v>
       </c>
       <c r="I99" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J99" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="K99">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L99">
-        <v>0.04</v>
-      </c>
-      <c r="M99">
-        <v>1032.75</v>
-      </c>
-      <c r="N99">
-        <v>17.55</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
+        <v>1.9760946303193187E-2</v>
       </c>
       <c r="P99">
-        <v>1</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="Q99">
-        <v>0.23354545132238788</v>
+        <v>0.2386419197277922</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B100" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="C100" t="s">
         <v>48</v>
@@ -10358,16 +10715,16 @@
         <v>3</v>
       </c>
       <c r="E100">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="I100" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J100" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="K100">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L100">
         <v>0.04</v>
@@ -10385,12 +10742,12 @@
         <v>1</v>
       </c>
       <c r="Q100">
-        <v>0.22878422375200849</v>
+        <v>0.2301224015067071</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B101" t="s">
         <v>128</v>
@@ -10402,25 +10759,25 @@
         <v>3</v>
       </c>
       <c r="E101">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="I101" t="s">
         <v>129</v>
       </c>
       <c r="J101" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K101">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L101">
-        <v>5.3999999999999999E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M101">
-        <v>879.75</v>
+        <v>1032.75</v>
       </c>
       <c r="N101">
-        <v>14.85</v>
+        <v>17.55</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -10429,12 +10786,12 @@
         <v>1</v>
       </c>
       <c r="Q101">
-        <v>0.2357479849120028</v>
+        <v>0.25369869095953879</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B102" t="s">
         <v>128</v>
@@ -10446,19 +10803,19 @@
         <v>3</v>
       </c>
       <c r="E102">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="I102" t="s">
         <v>129</v>
       </c>
       <c r="J102" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="K102">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="L102">
-        <v>3.2000000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M102">
         <v>1032.75</v>
@@ -10473,42 +10830,42 @@
         <v>1</v>
       </c>
       <c r="Q102">
-        <v>0.24195369464045599</v>
+        <v>0.25369869095953879</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B103" t="s">
         <v>128</v>
       </c>
       <c r="C103" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D103" t="s">
         <v>3</v>
       </c>
       <c r="E103">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I103" t="s">
         <v>129</v>
       </c>
       <c r="J103" t="s">
-        <v>122</v>
+        <v>229</v>
       </c>
       <c r="K103">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L103">
-        <v>3.5999999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M103">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="N103">
-        <v>46.800000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -10517,42 +10874,42 @@
         <v>1</v>
       </c>
       <c r="Q103">
-        <v>0.33309194745150211</v>
+        <v>0.25369869095953879</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B104" t="s">
         <v>128</v>
       </c>
       <c r="C104" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D104" t="s">
         <v>3</v>
       </c>
       <c r="E104">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="I104" t="s">
         <v>129</v>
       </c>
       <c r="J104" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="K104">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L104">
-        <v>0.05</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="M104">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="N104">
-        <v>46.8</v>
+        <v>17.55</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -10561,42 +10918,42 @@
         <v>1</v>
       </c>
       <c r="Q104">
-        <v>0.4985435282620107</v>
+        <v>0.23354545132238791</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="B105" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="C105" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D105" t="s">
         <v>3</v>
       </c>
       <c r="E105">
-        <v>2013</v>
+        <v>2028</v>
       </c>
       <c r="I105" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J105" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="K105">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L105">
-        <v>1.4E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M105">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="N105">
-        <v>46.800000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -10605,42 +10962,42 @@
         <v>1</v>
       </c>
       <c r="Q105">
-        <v>9.9312871764815305E-2</v>
+        <v>0.23354545132238788</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B106" t="s">
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D106" t="s">
         <v>3</v>
       </c>
       <c r="E106">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="I106" t="s">
         <v>129</v>
       </c>
       <c r="J106" t="s">
-        <v>58</v>
+        <v>232</v>
       </c>
       <c r="K106">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L106">
-        <v>1.15E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M106">
-        <v>1836</v>
+        <v>1032.75</v>
       </c>
       <c r="N106">
-        <v>46.800000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -10649,42 +11006,42 @@
         <v>1</v>
       </c>
       <c r="Q106">
-        <v>9.9312871764815305E-2</v>
+        <v>0.22878422375200849</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B107" t="s">
         <v>128</v>
       </c>
       <c r="C107" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D107" t="s">
         <v>3</v>
       </c>
       <c r="E107">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="I107" t="s">
         <v>129</v>
       </c>
       <c r="J107" t="s">
-        <v>58</v>
+        <v>234</v>
       </c>
       <c r="K107">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L107">
-        <v>0.161</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="M107">
-        <v>1667.0559006211181</v>
+        <v>879.75</v>
       </c>
       <c r="N107">
-        <v>42.327950310559004</v>
+        <v>14.85</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -10693,45 +11050,42 @@
         <v>1</v>
       </c>
       <c r="Q107">
-        <v>9.9312871764815319E-2</v>
+        <v>0.2357479849120028</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B108" t="s">
-        <v>241</v>
+        <v>128</v>
       </c>
       <c r="C108" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D108" t="s">
         <v>3</v>
       </c>
       <c r="E108">
-        <v>2019</v>
-      </c>
-      <c r="G108" t="s">
-        <v>242</v>
+        <v>2022</v>
       </c>
       <c r="I108" t="s">
         <v>129</v>
       </c>
       <c r="J108" t="s">
-        <v>63</v>
+        <v>236</v>
       </c>
       <c r="K108">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="L108">
-        <v>0.26</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="M108">
-        <v>1563.9999999999998</v>
+        <v>1032.75</v>
       </c>
       <c r="N108">
-        <v>39.6</v>
+        <v>17.55</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -10740,15 +11094,15 @@
         <v>1</v>
       </c>
       <c r="Q108">
-        <v>0.49854352826201065</v>
+        <v>0.24195369464045599</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B109" t="s">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="C109" t="s">
         <v>53</v>
@@ -10757,28 +11111,25 @@
         <v>3</v>
       </c>
       <c r="E109">
-        <v>2028</v>
-      </c>
-      <c r="H109" t="s">
-        <v>245</v>
+        <v>2021</v>
       </c>
       <c r="I109" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J109" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="K109">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L109">
-        <v>0.3</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="M109">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="N109">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -10787,6 +11138,276 @@
         <v>1</v>
       </c>
       <c r="Q109">
+        <v>0.33309194745150211</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" t="s">
+        <v>128</v>
+      </c>
+      <c r="C110" t="s">
+        <v>53</v>
+      </c>
+      <c r="D110" t="s">
+        <v>3</v>
+      </c>
+      <c r="E110">
+        <v>2019</v>
+      </c>
+      <c r="I110" t="s">
+        <v>129</v>
+      </c>
+      <c r="J110" t="s">
+        <v>63</v>
+      </c>
+      <c r="K110">
+        <v>13</v>
+      </c>
+      <c r="L110">
+        <v>0.05</v>
+      </c>
+      <c r="M110">
+        <v>1836</v>
+      </c>
+      <c r="N110">
+        <v>46.8</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>1</v>
+      </c>
+      <c r="Q110">
+        <v>0.4985435282620107</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" t="s">
+        <v>128</v>
+      </c>
+      <c r="C111" t="s">
+        <v>53</v>
+      </c>
+      <c r="D111" t="s">
+        <v>3</v>
+      </c>
+      <c r="E111">
+        <v>2013</v>
+      </c>
+      <c r="I111" t="s">
+        <v>129</v>
+      </c>
+      <c r="J111" t="s">
+        <v>58</v>
+      </c>
+      <c r="K111">
+        <v>22</v>
+      </c>
+      <c r="L111">
+        <v>1.4E-2</v>
+      </c>
+      <c r="M111">
+        <v>1836</v>
+      </c>
+      <c r="N111">
+        <v>46.800000000000004</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>1</v>
+      </c>
+      <c r="Q111">
+        <v>9.9312871764815305E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" t="s">
+        <v>128</v>
+      </c>
+      <c r="C112" t="s">
+        <v>53</v>
+      </c>
+      <c r="D112" t="s">
+        <v>3</v>
+      </c>
+      <c r="E112">
+        <v>2015</v>
+      </c>
+      <c r="I112" t="s">
+        <v>129</v>
+      </c>
+      <c r="J112" t="s">
+        <v>58</v>
+      </c>
+      <c r="K112">
+        <v>22</v>
+      </c>
+      <c r="L112">
+        <v>1.15E-2</v>
+      </c>
+      <c r="M112">
+        <v>1836</v>
+      </c>
+      <c r="N112">
+        <v>46.800000000000004</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+      <c r="Q112">
+        <v>9.9312871764815305E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>239</v>
+      </c>
+      <c r="B113" t="s">
+        <v>128</v>
+      </c>
+      <c r="C113" t="s">
+        <v>53</v>
+      </c>
+      <c r="D113" t="s">
+        <v>3</v>
+      </c>
+      <c r="E113">
+        <v>2021</v>
+      </c>
+      <c r="I113" t="s">
+        <v>129</v>
+      </c>
+      <c r="J113" t="s">
+        <v>58</v>
+      </c>
+      <c r="K113">
+        <v>22</v>
+      </c>
+      <c r="L113">
+        <v>0.161</v>
+      </c>
+      <c r="M113">
+        <v>1667.0559006211181</v>
+      </c>
+      <c r="N113">
+        <v>42.327950310559004</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>1</v>
+      </c>
+      <c r="Q113">
+        <v>9.9312871764815319E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>240</v>
+      </c>
+      <c r="B114" t="s">
+        <v>241</v>
+      </c>
+      <c r="C114" t="s">
+        <v>53</v>
+      </c>
+      <c r="D114" t="s">
+        <v>3</v>
+      </c>
+      <c r="E114">
+        <v>2019</v>
+      </c>
+      <c r="G114" t="s">
+        <v>242</v>
+      </c>
+      <c r="I114" t="s">
+        <v>129</v>
+      </c>
+      <c r="J114" t="s">
+        <v>63</v>
+      </c>
+      <c r="K114">
+        <v>13</v>
+      </c>
+      <c r="L114">
+        <v>0.26</v>
+      </c>
+      <c r="M114">
+        <v>1563.9999999999998</v>
+      </c>
+      <c r="N114">
+        <v>39.6</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>1</v>
+      </c>
+      <c r="Q114">
+        <v>0.49854352826201065</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>243</v>
+      </c>
+      <c r="B115" t="s">
+        <v>244</v>
+      </c>
+      <c r="C115" t="s">
+        <v>53</v>
+      </c>
+      <c r="D115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E115">
+        <v>2028</v>
+      </c>
+      <c r="H115" t="s">
+        <v>245</v>
+      </c>
+      <c r="I115" t="s">
+        <v>132</v>
+      </c>
+      <c r="J115" t="s">
+        <v>54</v>
+      </c>
+      <c r="K115">
+        <v>11</v>
+      </c>
+      <c r="L115">
+        <v>0.3</v>
+      </c>
+      <c r="M115">
+        <v>1563.9999999999998</v>
+      </c>
+      <c r="N115">
+        <v>39.6</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>1</v>
+      </c>
+      <c r="Q115">
         <v>0.3404851337933279</v>
       </c>
     </row>

--- a/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
+++ b/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE5B1CB0-CA77-4B28-A1B4-13C4E2B6EC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9D264D1-CE08-40EF-8930-3A4475E4E614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="38" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="37" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="36" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="35" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="34" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="43" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="42" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="41" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="40" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="39" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1438,7 +1438,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94689CB2-40D7-8D8C-F753-FF4F04ECEA98}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CF81FE-561E-BAF6-DEDD-AEC0692DAE2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1493,7 +1493,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB90FBAE-984D-EE28-6E99-EAE3AE39B7F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF073AA8-5027-D614-8FF4-7D916C8E3E48}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1844,7 +1844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A6B2D4-B78E-47AD-96A4-D2DA35248C0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01116BC8-405D-4343-85D8-2ECCF1AAF17B}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4972,7 +4972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0A268F1-7B72-4A73-A2E6-D8552CD961AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B229767-5CB2-40DB-8335-2C113AA27387}">
   <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5582,7 +5582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523B0D75-838B-446A-A3FF-CFFC6BDAD3A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB15E632-382A-49EE-8D5B-3CDBBF225279}">
   <dimension ref="B2:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5858,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A637E6B6-466B-4A36-B060-72618466DD4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C57A42C-B009-4E2C-9982-50CA65BE2DC1}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6313,7 +6313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89704539-7958-4D2A-B729-A9BD7F41AF1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A372BA8-56FE-42B1-BA02-8769ABB549C9}">
   <dimension ref="A1:Y115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
+++ b/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9D264D1-CE08-40EF-8930-3A4475E4E614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EEACEE7-AEE2-4988-9A48-8CBD08C1F3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="43" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="42" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="41" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="40" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="39" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="48" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="47" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="46" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="45" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="44" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1438,7 +1438,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32CF81FE-561E-BAF6-DEDD-AEC0692DAE2D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91D14789-2383-E2CB-AC08-5F44413269A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1493,7 +1493,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF073AA8-5027-D614-8FF4-7D916C8E3E48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E58D8D0-DE67-5CBA-86AA-D2A484D8BC3A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1844,7 +1844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01116BC8-405D-4343-85D8-2ECCF1AAF17B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA9C54B-A178-47DB-B798-6343BF2F8579}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4972,7 +4972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B229767-5CB2-40DB-8335-2C113AA27387}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30FD679-8A36-4150-8B70-3738B2D77737}">
   <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5582,7 +5582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB15E632-382A-49EE-8D5B-3CDBBF225279}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C3CF85-5476-4007-B875-6A7727EECE81}">
   <dimension ref="B2:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5858,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C57A42C-B009-4E2C-9982-50CA65BE2DC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE3D611-E8FD-4A5A-80A3-D3A3683276A4}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6313,7 +6313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A372BA8-56FE-42B1-BA02-8769ABB549C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B49AC76-08D0-4338-ADE2-289E34E9728C}">
   <dimension ref="A1:Y115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
+++ b/VerveStacks_KEN_grids_kan/source_data/VerveStacks_KEN.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EEACEE7-AEE2-4988-9A48-8CBD08C1F3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3B5EEBF-BDBA-49FA-8D55-5F6C3C2FE580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="48" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="47" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="46" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="45" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="44" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="53" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="52" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="51" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="50" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="49" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -1438,7 +1438,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91D14789-2383-E2CB-AC08-5F44413269A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B33BA6AA-1637-5A2A-3B8E-34913A921696}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1493,7 +1493,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E58D8D0-DE67-5CBA-86AA-D2A484D8BC3A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{936C1BC9-9BDE-8958-0DEA-CC8185C6A208}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1844,7 +1844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA9C54B-A178-47DB-B798-6343BF2F8579}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E2999B-9C68-403B-8979-77C813774736}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4972,7 +4972,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B30FD679-8A36-4150-8B70-3738B2D77737}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF96E764-8B9C-4C81-B457-E54C88BE3466}">
   <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5582,7 +5582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2C3CF85-5476-4007-B875-6A7727EECE81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{523F361F-5E7F-44B9-AF8A-4273096D1C6D}">
   <dimension ref="B2:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5858,7 +5858,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DE3D611-E8FD-4A5A-80A3-D3A3683276A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB9535B-65E4-4B07-9A79-A89062260716}">
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6313,7 +6313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B49AC76-08D0-4338-ADE2-289E34E9728C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E57BEF-F80B-418C-AF90-2254E8B23907}">
   <dimension ref="A1:Y115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
